--- a/www/terminologies/ValueSet-JDV-J186-ProfessionRessource-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J186-ProfessionRessource-ROR.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="303">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250710120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-10T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -918,6 +918,12 @@
   </si>
   <si>
     <t>Intermédiateur</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Stomathérapeute</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
@@ -1788,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2581,18 +2587,26 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>86</v>
+        <v>301</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B100" t="s" s="2">
-        <v>300</v>
+      <c r="B101" t="s" s="2">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
